--- a/assets/excel/fundamental of programming/AttendanceSheet8.xlsx
+++ b/assets/excel/fundamental of programming/AttendanceSheet8.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fci mobile project\Attendance\assets\excel\fundamental of programming\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nerme\Downloads\excel\Algorithmes\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C06630C-8087-455D-BF9D-6C6270C9D649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11160"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXPORT_FACE_ATTENDANCE-20240818" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -876,7 +877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
